--- a/orders.xlsx
+++ b/orders.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
   <si>
     <t>ID</t>
   </si>
@@ -120,6 +120,30 @@
   </si>
   <si>
     <t>М020УР97</t>
+  </si>
+  <si>
+    <t>Тойота Камри</t>
+  </si>
+  <si>
+    <t>С111КР97</t>
+  </si>
+  <si>
+    <t>Замена колес</t>
+  </si>
+  <si>
+    <t>2026-09-17T11:05:47.467193</t>
+  </si>
+  <si>
+    <t>Мерседес ГЛС</t>
+  </si>
+  <si>
+    <t>А989МР97</t>
+  </si>
+  <si>
+    <t>Подкачка шин</t>
+  </si>
+  <si>
+    <t>2026-09-17T11:14:16.729895</t>
   </si>
 </sst>
 </file>
@@ -164,7 +188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="2.8984375" customWidth="true" bestFit="true"/>
@@ -437,6 +461,58 @@
         <v>5.0</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F11" t="n" s="0">
+        <v>3000.0</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="H11" t="n" s="0">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F12" t="n" s="0">
+        <v>1000.0</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="H12" t="n" s="0">
+        <v>7.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
